--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0001.xlsx
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
